--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1173387</v>
+        <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>92497</v>
+        <v>96688</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,34 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3884</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Testa, Nrk</t>
+          <t>Testa, lövskog 500 m SO om, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521324</v>
+        <v>521309</v>
       </c>
       <c r="R6" t="n">
-        <v>6553489</v>
+        <v>6553464</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-11-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-11-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,35 +1241,30 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>ek/hasselskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>hassel</t>
+          <t>fuktig lövskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1173387</t>
+          <t>https://artportalen.se/Sighting/136960820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1173388</v>
+        <v>1173387</v>
       </c>
       <c r="B7" t="n">
         <v>92497</v>
@@ -1304,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521319</v>
+        <v>521324</v>
       </c>
       <c r="R7" t="n">
-        <v>6553486</v>
+        <v>6553489</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1375,13 +1370,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1173388</t>
+          <t>https://artportalen.se/Sighting/1173387</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129096601</v>
+        <v>1173388</v>
       </c>
       <c r="B8" t="n">
         <v>92497</v>
@@ -1412,17 +1407,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521492</v>
+        <v>521319</v>
       </c>
       <c r="R8" t="n">
-        <v>6553127</v>
+        <v>6553486</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2011-11-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2011-11-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,38 +1460,38 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Lövskog på kalkrik mark</t>
+          <t>ek/hasselskog</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>på nedfallen hasselgren</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096601</t>
+          <t>https://artportalen.se/Sighting/1173388</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129259884</v>
+        <v>129096601</v>
       </c>
       <c r="B9" t="n">
-        <v>81655</v>
+        <v>92497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,34 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3929</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521338</v>
+        <v>521492</v>
       </c>
       <c r="R9" t="n">
-        <v>6553500</v>
+        <v>6553127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,12 +1553,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,87 +1572,73 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>lövskog</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>hassel</t>
+          <t>Lövskog på kalkrik mark</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>hassel</t>
+          <t>på nedfallen hasselgren</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Michael Andersson, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129259884</t>
+          <t>https://artportalen.se/Sighting/129096601</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096617</v>
+        <v>129259884</v>
       </c>
       <c r="B10" t="n">
-        <v>91867</v>
+        <v>81655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5445</v>
+        <v>3929</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Roth.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, skog SO om, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521470</v>
+        <v>521338</v>
       </c>
       <c r="R10" t="n">
-        <v>6553226</v>
+        <v>6553500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,12 +1665,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,73 +1684,87 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Lövskog på kalkrik mark</t>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på ek</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096617</t>
+          <t>https://artportalen.se/Sighting/129259884</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096573</v>
+        <v>129096617</v>
       </c>
       <c r="B11" t="n">
-        <v>89902</v>
+        <v>91867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5581</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521431</v>
+        <v>521470</v>
       </c>
       <c r="R11" t="n">
-        <v>6553183</v>
+        <v>6553226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1805,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1821,7 +1815,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>lövved</t>
+          <t>på ek</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1838,16 +1832,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096573</t>
+          <t>https://artportalen.se/Sighting/129096617</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133622986</v>
+        <v>129096573</v>
       </c>
       <c r="B12" t="n">
-        <v>107690</v>
+        <v>89902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,46 +1849,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219686</v>
+        <v>5581</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Britzelm.) Sacc.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521370</v>
+        <v>521431</v>
       </c>
       <c r="R12" t="n">
-        <v>6553485</v>
+        <v>6553183</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1918,12 +1903,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,35 +1917,41 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Ädellövskog, tidigare ekhage</t>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>lövved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622986</t>
+          <t>https://artportalen.se/Sighting/129096573</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133622988</v>
+        <v>133622986</v>
       </c>
       <c r="B13" t="n">
         <v>107690</v>
@@ -1990,7 +1981,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2004,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521357</v>
+        <v>521370</v>
       </c>
       <c r="R13" t="n">
-        <v>6553478</v>
+        <v>6553485</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2070,13 +2061,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622988</t>
+          <t>https://artportalen.se/Sighting/133622986</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133622989</v>
+        <v>133622988</v>
       </c>
       <c r="B14" t="n">
         <v>107690</v>
@@ -2106,7 +2097,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2120,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521397</v>
+        <v>521357</v>
       </c>
       <c r="R14" t="n">
-        <v>6553453</v>
+        <v>6553478</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2186,13 +2177,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622989</t>
+          <t>https://artportalen.se/Sighting/133622988</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133622990</v>
+        <v>133622989</v>
       </c>
       <c r="B15" t="n">
         <v>107690</v>
@@ -2236,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521393</v>
+        <v>521397</v>
       </c>
       <c r="R15" t="n">
-        <v>6553446</v>
+        <v>6553453</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2302,13 +2293,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622990</t>
+          <t>https://artportalen.se/Sighting/133622989</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133622991</v>
+        <v>133622990</v>
       </c>
       <c r="B16" t="n">
         <v>107690</v>
@@ -2338,7 +2329,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2352,10 +2343,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521383</v>
+        <v>521393</v>
       </c>
       <c r="R16" t="n">
-        <v>6553441</v>
+        <v>6553446</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2418,13 +2409,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622991</t>
+          <t>https://artportalen.se/Sighting/133622990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622992</v>
+        <v>133622991</v>
       </c>
       <c r="B17" t="n">
         <v>107690</v>
@@ -2454,7 +2445,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2468,10 +2459,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521391</v>
+        <v>521383</v>
       </c>
       <c r="R17" t="n">
-        <v>6553439</v>
+        <v>6553441</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2534,13 +2525,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622992</t>
+          <t>https://artportalen.se/Sighting/133622991</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623000</v>
+        <v>133622992</v>
       </c>
       <c r="B18" t="n">
         <v>107690</v>
@@ -2584,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521425</v>
+        <v>521391</v>
       </c>
       <c r="R18" t="n">
-        <v>6553358</v>
+        <v>6553439</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2650,33 +2641,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133623000</t>
+          <t>https://artportalen.se/Sighting/133622992</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082719</v>
+        <v>133623000</v>
       </c>
       <c r="B19" t="n">
-        <v>106812</v>
+        <v>107690</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>219686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2684,24 +2675,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skogsberg N om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521498</v>
+        <v>521425</v>
       </c>
       <c r="R19" t="n">
-        <v>6553177</v>
+        <v>6553358</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2725,12 +2721,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,31 +2735,35 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129082719</t>
+          <t>https://artportalen.se/Sighting/133623000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254787</v>
+        <v>129082719</v>
       </c>
       <c r="B20" t="n">
         <v>106812</v>
@@ -2792,19 +2792,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Skogsberg N om, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521397</v>
+        <v>521498</v>
       </c>
       <c r="R20" t="n">
-        <v>6553357</v>
+        <v>6553177</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,12 +2832,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,35 +2846,31 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Lövskog på kalkrik mark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129254787</t>
+          <t>https://artportalen.se/Sighting/129082719</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129260020</v>
+        <v>129254787</v>
       </c>
       <c r="B21" t="n">
         <v>106812</v>
@@ -2901,17 +2901,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521332</v>
+        <v>521397</v>
       </c>
       <c r="R21" t="n">
-        <v>6553404</v>
+        <v>6553357</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,13 +2954,13 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Lövskog på kalkrik mark</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2971,13 +2971,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129260020</t>
+          <t>https://artportalen.se/Sighting/129254787</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129260021</v>
+        <v>129260020</v>
       </c>
       <c r="B22" t="n">
         <v>106812</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521411</v>
+        <v>521332</v>
       </c>
       <c r="R22" t="n">
-        <v>6553315</v>
+        <v>6553404</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3078,13 +3078,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129260021</t>
+          <t>https://artportalen.se/Sighting/129260020</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129260022</v>
+        <v>129260021</v>
       </c>
       <c r="B23" t="n">
         <v>106812</v>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521374</v>
+        <v>521411</v>
       </c>
       <c r="R23" t="n">
-        <v>6553324</v>
+        <v>6553315</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3185,33 +3185,33 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129260022</t>
+          <t>https://artportalen.se/Sighting/129260021</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129259940</v>
+        <v>129260022</v>
       </c>
       <c r="B24" t="n">
-        <v>106155</v>
+        <v>106812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521340</v>
+        <v>521374</v>
       </c>
       <c r="R24" t="n">
-        <v>6553375</v>
+        <v>6553324</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3292,33 +3292,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129259940</t>
+          <t>https://artportalen.se/Sighting/129260022</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133622996</v>
+        <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>106236</v>
+        <v>107064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3326,29 +3326,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, lövskog 500 m SO om, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521367</v>
+        <v>521331</v>
       </c>
       <c r="R25" t="n">
-        <v>6553307</v>
+        <v>6553402</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3372,12 +3363,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,33 +3382,33 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Ädellövskog, tidigare ekhage</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622996</t>
+          <t>https://artportalen.se/Sighting/136961237</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122905355</v>
+        <v>129259940</v>
       </c>
       <c r="B26" t="n">
-        <v>101326</v>
+        <v>106155</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,45 +3416,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Testaskogen, Nrk</t>
+          <t>Testa, skog SO om, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521375</v>
+        <v>521340</v>
       </c>
       <c r="R26" t="n">
-        <v>6553266</v>
+        <v>6553375</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3487,22 +3470,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3513,31 +3486,36 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122905355</t>
+          <t>https://artportalen.se/Sighting/129259940</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129096578</v>
+        <v>133622996</v>
       </c>
       <c r="B27" t="n">
-        <v>101325</v>
+        <v>106236</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3545,37 +3523,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521465</v>
+        <v>521367</v>
       </c>
       <c r="R27" t="n">
-        <v>6553182</v>
+        <v>6553307</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3599,12 +3586,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3618,33 +3605,33 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Lövskog på kalkrik mark</t>
+          <t>Ädellövskog, tidigare ekhage</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096578</t>
+          <t>https://artportalen.se/Sighting/133622996</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129096599</v>
+        <v>122905355</v>
       </c>
       <c r="B28" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3670,19 +3657,27 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testaskogen, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521497</v>
+        <v>521375</v>
       </c>
       <c r="R28" t="n">
-        <v>6553139</v>
+        <v>6553266</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3706,12 +3701,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3722,33 +3727,28 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Lövskog på kalkrik mark</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096599</t>
+          <t>https://artportalen.se/Sighting/122905355</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129096607</v>
+        <v>129096578</v>
       </c>
       <c r="B29" t="n">
         <v>101325</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521476</v>
+        <v>521465</v>
       </c>
       <c r="R29" t="n">
-        <v>6553172</v>
+        <v>6553182</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3849,13 +3849,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096607</t>
+          <t>https://artportalen.se/Sighting/129096578</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129259996</v>
+        <v>129096599</v>
       </c>
       <c r="B30" t="n">
         <v>101325</v>
@@ -3886,17 +3886,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521332</v>
+        <v>521497</v>
       </c>
       <c r="R30" t="n">
-        <v>6553404</v>
+        <v>6553139</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3920,12 +3920,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3939,30 +3939,30 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Lövskog på kalkrik mark</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Michael Andersson, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129259996</t>
+          <t>https://artportalen.se/Sighting/129096599</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129259998</v>
+        <v>129096607</v>
       </c>
       <c r="B31" t="n">
         <v>101325</v>
@@ -3993,14 +3993,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521340</v>
+        <v>521476</v>
       </c>
       <c r="R31" t="n">
-        <v>6553375</v>
+        <v>6553172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,33 +4046,33 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Lövskog på kalkrik mark</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Michael Andersson, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129259998</t>
+          <t>https://artportalen.se/Sighting/129096607</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096594</v>
+        <v>129259996</v>
       </c>
       <c r="B32" t="n">
-        <v>101227</v>
+        <v>101325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4080,37 +4080,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, skog SO om, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521437</v>
+        <v>521332</v>
       </c>
       <c r="R32" t="n">
-        <v>6553126</v>
+        <v>6553404</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4153,33 +4153,33 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Lövskog på kalkrik mark</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096594</t>
+          <t>https://artportalen.se/Sighting/129259996</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133622985</v>
+        <v>129259998</v>
       </c>
       <c r="B33" t="n">
-        <v>99001</v>
+        <v>101325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4187,46 +4187,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, skog SO om, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521357</v>
+        <v>521340</v>
       </c>
       <c r="R33" t="n">
-        <v>6553514</v>
+        <v>6553375</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4250,12 +4241,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,33 +4260,33 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Ädellövskog, tidigare ekhage</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622985</t>
+          <t>https://artportalen.se/Sighting/129259998</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133622987</v>
+        <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>99001</v>
+        <v>101563</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4303,46 +4294,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, lövskog 500 m SO om, Nrk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521347</v>
+        <v>521331</v>
       </c>
       <c r="R34" t="n">
-        <v>6553484</v>
+        <v>6553402</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4366,12 +4348,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4385,33 +4367,33 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Ädellövskog, tidigare ekhage</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622987</t>
+          <t>https://artportalen.se/Sighting/136961208</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133622993</v>
+        <v>129096594</v>
       </c>
       <c r="B35" t="n">
-        <v>99001</v>
+        <v>101227</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4419,16 +4401,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4436,29 +4418,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521361</v>
+        <v>521437</v>
       </c>
       <c r="R35" t="n">
-        <v>6553380</v>
+        <v>6553126</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4482,12 +4455,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,30 +4474,30 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Ädellövskog, tidigare ekhage</t>
+          <t>Lövskog på kalkrik mark</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622993</t>
+          <t>https://artportalen.se/Sighting/129096594</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133622999</v>
+        <v>133622985</v>
       </c>
       <c r="B36" t="n">
         <v>99001</v>
@@ -4554,7 +4527,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4568,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521427</v>
+        <v>521357</v>
       </c>
       <c r="R36" t="n">
-        <v>6553249</v>
+        <v>6553514</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4633,6 +4606,354 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622985</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133622987</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>521347</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6553484</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622987</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133622993</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>521361</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6553380</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622993</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133622999</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>521427</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6553249</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133622999</t>
         </is>
@@ -4675,6 +4996,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107158</v>
+        <v>107160</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136960820</v>
       </c>
       <c r="B6" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>136961237</v>
       </c>
       <c r="B25" t="n">
-        <v>107160</v>
+        <v>107164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>136961208</v>
       </c>
       <c r="B34" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
